--- a/AI Audit Log_Ngô Tấn Hưng.xlsx
+++ b/AI Audit Log_Ngô Tấn Hưng.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_IT\Semester\SU26\SE20C02_LAB211_SU26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE lerning\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C0687-CA9D-4246-B1F8-DF53106083A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -18,52 +18,17 @@
     <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
     <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Ví dụ: Abstraction</t>
-  </si>
-  <si>
-    <t>“Tôi cần quản lý thông tin sinh viên cho app quản lý điểm. Hãy liệt kê các thuộc tính cần thiết."</t>
-  </si>
-  <si>
-    <t>Ví dụ: Process/Algorithm</t>
-  </si>
-  <si>
-    <t>Ví dụ: Pattern Recognition</t>
-  </si>
-  <si>
-    <t>“So sánh các giải thuật CPU scheduling: FCFS, SJF, Round Robin, Priority. Giải thuật nào tốt nhất?”</t>
-  </si>
-  <si>
-    <t>Ví dụ: Pattern Recognition + Literature Review</t>
-  </si>
-  <si>
-    <t>“Tóm tắt 5 bài báo gần đây nhất về anomaly detection trong IoT sensor data.”</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -77,23 +42,97 @@
     <t>STT</t>
   </si>
   <si>
-    <t>Phản hồi: AI liệt kê 20 thuộc tính.
-Quyết định: Tôi chỉ chọn 10 thuộc tính liên quan đến chức năng đang được yêu cầu từ ứng dụng (CCCD, địa chỉ...) và lược bỏ 10 thuộc tính học thuật vì phù hợp với yêu cầu của ứng dụng</t>
-  </si>
-  <si>
-    <t>"Viết hàm C sắp xếp mảng sinh viên theo điểm số bằng Selection Sort."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp code mẫu.
-Kiểm chứng: Tôi nhận thấy code AI chưa xử lý trường hợp mảng rỗng (Oversimplification). Tôi đã yêu cầu AI tối ưu lại và tự tay bổ sung điều kiện kiểm tra lỗi.</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI response Round Robin là “tốt nhất” vì cân bằng giữa throughput và fairness.
-Kiểm chứng: AI đưa kết luận sai – không có giải thuật “tốt nhất” tuyệt đối (Hallucination). Mỗi giải thuật phù hợp với tình huống/context khác nhau.</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI tóm tắt 5 papers với tên tác giả, năm xuất bản và tóm tắt nội dung.
-Kiểm chứng: Tìm trên Google Scholar: 2/5 papers AI nêu là không tồn tại (fabrication). Tôi đã thay bằng 2 papers mà tôi đã tìm kiếm trên research gates và đã kiểm chứng trên google scholar.</t>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>“Liệt kê các actor và use case chính cho hệ thống quản lý sinh viên.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các actor gồm Student, Lecturer, Admin cùng khoảng 25 use case. Quyết định: Tôi nhận thấy một số use case bị trùng chức năng như “Manage Account” và “Update Profile”, nên đã gộp lại để sơ đồ dễ hiểu hơn.</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>“Phân rã chức năng ‘Course Registration’ thành các use case nhỏ hơn.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chia thành Search Course, Check Schedule, Check Prerequisite, Register Course, Cancel Registration. Quyết định: Tôi bổ sung thêm “View Registered Courses” vì cần thiết cho hệ thống thực tế.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>“So sánh use case diagram của hệ thống quản lý sinh viên và hệ thống thư viện.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ ra cả hai đều có Login, Manage User, Search Information. Quyết định: Tôi nhận ra nhiều hệ thống quản lý có mô hình use case tương tự nên có thể tái sử dụng cấu trúc phân tích.</t>
+  </si>
+  <si>
+    <t>Algorithm/Process</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn từng bước để xây dựng use case diagram cho website quản lý sinh viên.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đưa ra quy trình gồm xác định actor, xác định chức năng, nhóm chức năng và vẽ sơ đồ. Quyết định: Tôi áp dụng quy trình này để xây dựng sơ đồ use case có tổ chức hơn thay vì liệt kê ngẫu nhiên.</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>“Kiểm tra xem use case ‘Manage Student’ có quá tổng quát hay không.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho rằng use case này quá lớn và nên tách thành Add Student, Update Student, Delete Student, View Student. Quyết định: Tôi đồng ý và tách nhỏ để tăng tính rõ ràng cho sơ đồ.</t>
+  </si>
+  <si>
+    <t>“Đề xuất các chức năng cần thiết cho actor Lecturer trong hệ thống quản lý sinh viên.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Enter Grades, Upload Materials, View Schedule, Manage Attendance. Quyết định: Tôi loại bỏ “Upload Materials” vì hệ thống của tôi không hỗ trợ e-learning.</t>
+  </si>
+  <si>
+    <t>“Phân biệt include và extend trong use case diagram bằng ví dụ thực tế.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích include là chức năng bắt buộc còn extend là chức năng tùy chọn. Quyết định: Tôi dùng include cho ‘Validate Login’ và extend cho ‘Two-factor Authentication’.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra các lỗi thường gặp trong use case diagram này.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện một số lỗi như actor kết nối sai và use case đặt tên không bằng động từ. Quyết định: Tôi sửa lại tên thành các động từ như Login, Register Course, View Grades để đúng chuẩn UML.</t>
+  </si>
+  <si>
+    <t>Process/Algorithm</t>
+  </si>
+  <si>
+    <t>“Viết use case specification cho chức năng Login.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo đầy đủ các mục gồm Actor, Preconditions, Main Flow, Alternative Flow. Quyết định: Tôi chỉnh sửa phần Alternative Flow để bổ sung trường hợp tài khoản bị khóa sau nhiều lần nhập sai mật khẩu.</t>
+  </si>
+  <si>
+    <t>“Tách chức năng ‘Manage Course’ thành các chức năng con phù hợp.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Add Course, Update Course, Delete Course, Assign Lecturer. Quyết định: Tôi bổ sung thêm ‘View Course List’ vì người dùng cần xem danh sách môn học trước khi thao tác.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra tính hợp lý giữa actor Student và use case Enter Grades.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện Student không nên có quyền nhập điểm. Quyết định: Tôi sửa lại bằng cách chuyển use case này sang actor Lecturer để đảm bảo đúng phân quyền.</t>
+  </si>
+  <si>
+    <t>Abstraction + Reflection</t>
+  </si>
+  <si>
+    <t>“Đề xuất khoảng 40 use case cho hệ thống quản lý sinh viên.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê số lượng lớn use case nhưng có vài chức năng vượt quá phạm vi đề tài như Online Payment Gateway. Quyết định: Tôi chỉ chọn những use case phù hợp với scope của đồ án để tránh hệ thống quá phức tạp.</t>
   </si>
 </sst>
 </file>
@@ -115,6 +154,7 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -126,7 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -134,44 +174,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,84 +523,196 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.9296875" customWidth="1"/>
-    <col min="2" max="2" width="26.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="57" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -595,7 +723,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -604,7 +732,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -613,7 +741,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AI Audit Log_Ngô Tấn Hưng.xlsx
+++ b/AI Audit Log_Ngô Tấn Hưng.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE lerning\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C0687-CA9D-4246-B1F8-DF53106083A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E17363-810B-4CBA-BAC1-E475A66F939B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -133,6 +133,81 @@
   </si>
   <si>
     <t>Phản hồi: AI liệt kê số lượng lớn use case nhưng có vài chức năng vượt quá phạm vi đề tài như Online Payment Gateway. Quyết định: Tôi chỉ chọn những use case phù hợp với scope của đồ án để tránh hệ thống quá phức tạp.</t>
+  </si>
+  <si>
+    <t>“So sánh abstract class và interface trong class diagram.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích abstract class dùng cho kế thừa chung còn interface dùng để định nghĩa hành vi. Quyết định: Tôi sử dụng interface cho chức năng Loginable để nhiều class có thể triển khai linh hoạt.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra xem relationship giữa Order và Product có phù hợp không.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận thấy quan hệ trực tiếp many-to-many gây khó quản lý dữ liệu. Quyết định: Tôi thêm class OrderDetail làm lớp trung gian để lưu quantity và price.</t>
+  </si>
+  <si>
+    <t>“Liệt kê các class cần thiết cho hệ thống đặt vé xem phim.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Movie, Ticket, Customer, CinemaRoom, Showtime, Payment. Quyết định: Tôi loại bỏ class Promotion vì chưa nằm trong phạm vi yêu cầu của đồ án.</t>
+  </si>
+  <si>
+    <t>“Tách class Payment thành các class nhỏ hơn.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất CreditCardPayment, CashPayment, EWalletPayment. Quyết định: Tôi áp dụng inheritance để dễ mở rộng thêm phương thức thanh toán trong tương lai.</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn các bước xác định multiplicity trong class diagram.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích cách xác định one-to-one, one-to-many và many-to-many dựa trên nghiệp vụ hệ thống. Quyết định: Tôi sửa relationship giữa Lecturer và Course thành 1..* để đúng với thực tế giảng dạy.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra class diagram này có bị dư thừa class không.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện một số class có chức năng gần giống nhau như UserAccount và Account. Quyết định: Tôi gộp hai class này để giảm độ phức tạp của sơ đồ.</t>
+  </si>
+  <si>
+    <t>“Nhận diện các design pattern có thể áp dụng trong class diagram.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Singleton cho DatabaseConnection và Factory Method cho Payment creation. Quyết định: Tôi chỉ áp dụng Singleton vì phù hợp với quy mô hệ thống hiện tại.</t>
+  </si>
+  <si>
+    <t>“Đề xuất các method chính cho class ShoppingCart.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đưa ra addItem(), removeItem(), calculateTotal(), clearCart(). Quyết định: Tôi bổ sung updateQuantity() để hỗ trợ chỉnh sửa số lượng sản phẩm trong giỏ hàng.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra tính hợp lý của inheritance giữa Student và Course.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định đây là quan hệ sai vì Student không phải là một loại Course. Quyết định: Tôi thay inheritance bằng association giữa Student và Enrollment.</t>
+  </si>
+  <si>
+    <t>“Viết quy trình chuyển từ use case diagram sang class diagram.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn xác định entity từ use case, sau đó trích xuất thuộc tính và relationship. Quyết định: Tôi áp dụng cách này để xây dựng class diagram nhất quán với yêu cầu hệ thống.</t>
+  </si>
+  <si>
+    <t>“Phân rã class Library thành các class chức năng phù hợp.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất BookManager, UserManager, BorrowManager. Quyết định: Tôi đồng ý vì class Library ban đầu quá lớn và khó bảo trì.</t>
+  </si>
+  <si>
+    <t>Evaluation + Reflection</t>
+  </si>
+  <si>
+    <t>“Kiểm tra class diagram có tuân theo nguyên tắc SOLID không.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận thấy một số class đang phụ thuộc quá nhiều vào nhau (tight coupling). Quyết định: Tôi chỉnh sửa dependency và tách interface để giảm coupling và tăng khả năng mở rộng hệ thống.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
@@ -713,6 +788,174 @@
       </c>
       <c r="D13" s="3" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_Ngô Tấn Hưng.xlsx
+++ b/AI Audit Log_Ngô Tấn Hưng.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE lerning\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E17363-810B-4CBA-BAC1-E475A66F939B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78783D-CCE9-4424-9049-6E49C31604CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -208,13 +208,91 @@
   </si>
   <si>
     <t>Phản hồi: AI nhận thấy một số class đang phụ thuộc quá nhiều vào nhau (tight coupling). Quyết định: Tôi chỉnh sửa dependency và tách interface để giảm coupling và tăng khả năng mở rộng hệ thống.</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>“Giải thích các thành phần quan trọng của một prompt hiệu quả.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chia prompt thành Objective, Context, Constraint, Output Format và Example. Quyết định: Tôi nhận ra prompt càng rõ mục tiêu và định dạng thì kết quả AI trả về càng chính xác.</t>
+  </si>
+  <si>
+    <t>“So sánh prompt ngắn và prompt chi tiết khi yêu cầu AI viết use case.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho thấy prompt ngắn tạo output chung chung còn prompt chi tiết tạo kết quả sát yêu cầu hơn. Quyết định: Tôi ưu tiên viết prompt có context và yêu cầu cụ thể thay vì chỉ ghi vài từ khóa.</t>
+  </si>
+  <si>
+    <t>“Đánh giá prompt này: ‘Viết class diagram cho hệ thống quản lý sinh viên.’”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận xét prompt quá mơ hồ vì chưa nêu actor, phạm vi và định dạng output. Quyết định: Tôi bổ sung yêu cầu về class, relationship và PlantUML để AI trả lời đúng mục tiêu hơn.</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn từng bước để viết prompt hiệu quả cho ChatGPT.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất quy trình gồm xác định mục tiêu, cung cấp context, thêm constraint và yêu cầu output format. Quyết định: Tôi áp dụng cấu trúc này khi viết prompt cho UML và SRS.</t>
+  </si>
+  <si>
+    <t>“Phân tích prompt sau thành các phần nhỏ: ‘Viết use case specification cho chức năng Login bằng tiếng Anh theo chuẩn IEEE.’”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tách thành task, domain, language và standard format. Quyết định: Tôi hiểu rằng prompt tốt thường gồm nhiều thành phần rõ ràng thay vì một câu ngắn chung chung.</t>
+  </si>
+  <si>
+    <t>“Kiểm tra vì sao prompt của tôi cho output không đúng yêu cầu.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác định nguyên nhân do thiếu context và không chỉ rõ định dạng mong muốn. Quyết định: Tôi thêm ví dụ output và giới hạn phạm vi để cải thiện chất lượng phản hồi.</t>
+  </si>
+  <si>
+    <t>“Nhận diện các lỗi thường gặp khi viết prompt cho AI.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê các lỗi như prompt quá ngắn, mơ hồ, thiếu dữ liệu đầu vào hoặc yêu cầu quá nhiều nhiệm vụ cùng lúc. Quyết định: Tôi bắt đầu chia task lớn thành nhiều prompt nhỏ để AI xử lý chính xác hơn.</t>
+  </si>
+  <si>
+    <t>“Viết mẫu prompt chuẩn để yêu cầu AI tạo use case diagram.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tạo template gồm System Context, Actors, Functions, Constraints và Output Format. Quyết định: Tôi lưu template này để tái sử dụng cho các đồ án khác.</t>
+  </si>
+  <si>
+    <t>“So sánh kết quả giữa prompt có example và prompt không có example.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho thấy prompt có example giúp output đồng nhất và sát yêu cầu hơn. Quyết định: Tôi bắt đầu thêm ví dụ mẫu khi cần AI tạo tài liệu học thuật hoặc UML.</t>
+  </si>
+  <si>
+    <t>“Hướng dẫn cách viết prompt để AI sinh code PlantUML chính xác.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI khuyến nghị nêu rõ loại diagram, class/use case cần có và syntax PlantUML mong muốn. Quyết định: Tôi bổ sung các keyword như @startuml, relationship và multiplicity trong prompt để giảm lỗi syntax.</t>
+  </si>
+  <si>
+    <t>Reflection + Evaluation</t>
+  </si>
+  <si>
+    <t>“Phân tích vì sao AI đôi khi hallucination khi trả lời câu hỏi học thuật.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích hallucination thường xảy ra khi prompt quá chung chung hoặc thiếu nguồn dữ liệu rõ ràng. Quyết định: Tôi luôn kiểm chứng lại thông tin quan trọng thay vì sử dụng hoàn toàn output của AI.</t>
+  </si>
+  <si>
+    <t>“Đề xuất công thức viết prompt tối ưu cho học tập và làm đồ án.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất công thức: Role + Task + Context + Constraint + Output Format + Example. Quyết định: Tôi áp dụng cấu trúc này cho các prompt liên quan đến UML, testing và SRS để kết quả có tính học thuật và chính xác hơn.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +308,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -253,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -263,6 +349,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" customWidth="1"/>
@@ -620,7 +709,9 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
@@ -635,6 +726,9 @@
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
@@ -649,6 +743,9 @@
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -662,6 +759,9 @@
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -677,6 +777,9 @@
       <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
@@ -691,6 +794,9 @@
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
@@ -705,6 +811,9 @@
       <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -719,6 +828,9 @@
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
@@ -733,6 +845,9 @@
       <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
@@ -747,6 +862,9 @@
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
@@ -761,6 +879,9 @@
       <c r="D11" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
@@ -775,6 +896,9 @@
       <c r="D12" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
@@ -789,6 +913,9 @@
       <c r="D13" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
@@ -803,6 +930,9 @@
       <c r="D14" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
@@ -817,6 +947,9 @@
       <c r="D15" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
@@ -831,8 +964,11 @@
       <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -845,8 +981,11 @@
       <c r="D17" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -859,8 +998,11 @@
       <c r="D18" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -873,8 +1015,11 @@
       <c r="D19" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -887,8 +1032,11 @@
       <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -901,8 +1049,11 @@
       <c r="D21" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -915,8 +1066,11 @@
       <c r="D22" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -929,8 +1083,11 @@
       <c r="D23" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -943,8 +1100,11 @@
       <c r="D24" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -956,6 +1116,213 @@
       </c>
       <c r="D25" s="3" t="s">
         <v>59</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_Ngô Tấn Hưng.xlsx
+++ b/AI Audit Log_Ngô Tấn Hưng.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE lerning\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF008AE0-3F5A-4653-9E31-95D5A56B4341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742EE6BB-1A64-4EAA-AF97-5BC588D9EB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="6" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Week 3" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="2" r:id="rId4"/>
     <sheet name="Week 5" sheetId="3" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="8" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="236">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -617,6 +619,126 @@
   </si>
   <si>
     <t>Phản hồi: AI tổng hợp Layered Architecture, Microservices, Repository Pattern và Separation of Concerns. Quyết định: Tôi sử dụng các kiến thức này làm cơ sở thiết kế hệ thống AutoGo và các UML Diagram trong bài thi.</t>
+  </si>
+  <si>
+    <t>"Giải thích Activity Diagram là gì và mục đích sử dụng trong UML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Activity Diagram mô tả luồng công việc hoặc quy trình nghiệp vụ từ bắt đầu đến kết thúc. Quyết định: Tôi hiểu rằng sơ đồ này phù hợp để mô tả quy trình nghiệp vụ của hệ thống.</t>
+  </si>
+  <si>
+    <t>"Liệt kê các thành phần chính của Activity Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Initial Node, Action, Decision Node, Merge Node, Fork, Join và Final Node. Quyết định: Tôi ghi nhớ các ký hiệu UML cơ bản trước khi vẽ sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Activity Diagram và Sequence Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Activity Diagram tập trung vào luồng công việc, còn Sequence Diagram tập trung vào tương tác giữa các đối tượng theo thời gian. Quyết định: Tôi xác định đúng loại sơ đồ cần dùng cho từng yêu cầu bài tập.</t>
+  </si>
+  <si>
+    <t>"Giải thích ý nghĩa của Initial Node và Final Node."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Initial Node biểu thị điểm bắt đầu, còn Final Node biểu thị điểm kết thúc của quy trình. Quyết định: Tôi luôn đặt hai thành phần này vào Activity Diagram để thể hiện phạm vi quy trình.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Decision Node và Merge Node."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Decision Node dùng để rẽ nhánh điều kiện, còn Merge Node dùng để hợp nhất các nhánh lại thành một luồng. Quyết định: Tôi sử dụng đúng ký hiệu khi mô tả các điều kiện trong nghiệp vụ.</t>
+  </si>
+  <si>
+    <t>"Phân tích quy trình Create Booking thành các hoạt động nhỏ."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chia quy trình thành chọn xe, kiểm tra xe, tạo booking, thanh toán đặt cọc và xác nhận booking. Quyết định: Tôi sử dụng các bước này làm các Action trong Activity Diagram.</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn cách xây dựng Activity Diagram từ Use Case."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất xác định điểm bắt đầu, các hành động chính, điều kiện và điểm kết thúc. Quyết định: Tôi áp dụng quy trình này để xây dựng sơ đồ có cấu trúc rõ ràng.</t>
+  </si>
+  <si>
+    <t>"Khi nào nên sử dụng Guard Condition trong Activity Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Guard Condition được dùng để biểu diễn điều kiện trên các nhánh Decision. Quyết định: Tôi sử dụng các điều kiện như [Car Available] và [Payment Success].</t>
+  </si>
+  <si>
+    <t>"Kiểm tra luồng hoạt động có thiếu bước nghiệp vụ nào không."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện thiếu bước cập nhật trạng thái booking sau khi thanh toán. Quyết định: Tôi bổ sung bước Update Booking Status vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Giải thích ý nghĩa của Fork Node và Join Node."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Fork dùng để tách luồng xử lý song song và Join dùng để đồng bộ các luồng trước khi tiếp tục. Quyết định: Tôi sử dụng khi cần mô tả nhiều hoạt động xảy ra đồng thời.</t>
+  </si>
+  <si>
+    <t>"Khi nào cần sử dụng Activity Final thay vì Flow Final."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Activity Final kết thúc toàn bộ quy trình, còn Flow Final chỉ kết thúc một nhánh. Quyết định: Tôi lựa chọn loại Final Node phù hợp với mục tiêu mô hình hóa.</t>
+  </si>
+  <si>
+    <t>"Giải thích Swimlane trong Activity Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho rằng Swimlane giúp phân chia trách nhiệm giữa các tác nhân hoặc bộ phận trong quy trình. Quyết định: Tôi sử dụng Swimlane để phân biệt Customer và System.</t>
+  </si>
+  <si>
+    <t>"Xác định các Swimlane cho hệ thống thuê xe AutoGo."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Customer, Booking Service và Payment Service. Quyết định: Tôi áp dụng Swimlane để làm rõ trách nhiệm của từng thành phần.</t>
+  </si>
+  <si>
+    <t>"Mô tả luồng xử lý khi xe không khả dụng."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất chuyển sang nhánh thông báo lỗi và kết thúc quy trình. Quyết định: Tôi đưa luồng này vào nhánh điều kiện của Activity Diagram.</t>
+  </si>
+  <si>
+    <t>"Mô tả luồng xử lý khi thanh toán thất bại."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất hủy booking hoặc yêu cầu thanh toán lại. Quyết định: Tôi chọn hủy booking để đơn giản hóa sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra Activity Diagram có phản ánh đúng quy trình nghiệp vụ không."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận xét các bước chính đã đầy đủ nhưng cần bổ sung cập nhật trạng thái xe. Quyết định: Tôi thêm bước Update Vehicle Status sau khi booking được xác nhận.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Action và Activity trong UML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Activity là toàn bộ quy trình còn Action là một bước cụ thể trong quy trình đó. Quyết định: Tôi sử dụng các Action nhỏ để mô tả chi tiết luồng công việc.</t>
+  </si>
+  <si>
+    <t>"Những lỗi thường gặp khi vẽ Activity Diagram là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê các lỗi như thiếu điều kiện, sai hướng luồng, không có điểm bắt đầu hoặc kết thúc. Quyết định: Tôi sử dụng danh sách này như một checklist kiểm tra sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Tóm tắt các bước xây dựng Activity Diagram từ yêu cầu nghiệp vụ."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất xác định quy trình, hoạt động, điều kiện, Swimlane và điểm kết thúc. Quyết định: Tôi áp dụng quy trình này khi làm bài thi UML.</t>
+  </si>
+  <si>
+    <t>"Tổng kết kiến thức về Activity Diagram đã học."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tổng hợp Initial Node, Action, Decision, Merge, Fork, Join, Swimlane và Guard Condition. Quyết định: Tôi sử dụng các kiến thức này để thiết kế Activity Diagram đúng chuẩn UML và phản ánh chính xác quy trình nghiệp vụ.</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1573,7 @@
     <col min="4" max="4" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2424,4 +2546,322 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED1E0F3A-4EF6-4A86-BAA8-FB77E133628A}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73658DE-3F57-4E46-A9B0-8E52C14BF266}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_Ngô Tấn Hưng.xlsx
+++ b/AI Audit Log_Ngô Tấn Hưng.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE lerning\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742EE6BB-1A64-4EAA-AF97-5BC588D9EB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9B1476-FC3E-47DC-8A88-B6F79E4D9F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="276">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -739,6 +739,126 @@
   </si>
   <si>
     <t>Phản hồi: AI tổng hợp Initial Node, Action, Decision, Merge, Fork, Join, Swimlane và Guard Condition. Quyết định: Tôi sử dụng các kiến thức này để thiết kế Activity Diagram đúng chuẩn UML và phản ánh chính xác quy trình nghiệp vụ.</t>
+  </si>
+  <si>
+    <t>"Giải thích Component Diagram là gì và mục đích sử dụng trong UML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Component Diagram mô tả kiến trúc phần mềm ở mức cao, thể hiện các thành phần (components) và mối quan hệ phụ thuộc giữa chúng. Quyết định: Tôi hiểu rằng sơ đồ này giúp mô tả cấu trúc hệ thống thay vì chi tiết xử lý bên trong.</t>
+  </si>
+  <si>
+    <t>"Liệt kê các thành phần chính của Component Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Component, Interface, Dependency và Package. Quyết định: Tôi ghi nhớ các thành phần cơ bản trước khi xây dựng sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Component Diagram và Class Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Class Diagram mô tả cấu trúc lớp, còn Component Diagram mô tả các module hoặc thành phần lớn của hệ thống. Quyết định: Tôi xác định Component Diagram phù hợp hơn để mô tả kiến trúc phần mềm.</t>
+  </si>
+  <si>
+    <t>"Giải thích khái niệm Component trong UML."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Component là một đơn vị triển khai độc lập, cung cấp các chức năng cho hệ thống. Quyết định: Tôi xem Service, Repository và UI là các Component trong hệ thống AutoGo.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Provided Interface và Required Interface."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Provided Interface là dịch vụ component cung cấp, còn Required Interface là dịch vụ component cần sử dụng. Quyết định: Tôi sử dụng ký hiệu lollipop và socket đúng theo chuẩn UML.</t>
+  </si>
+  <si>
+    <t>"Phân tích hệ thống AutoGo thành các component chính."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất UI Component, Booking Service, Payment Service, Car Service, Repository Layer và Database. Quyết định: Tôi sử dụng các component này làm nền tảng cho sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn cách xây dựng Component Diagram từ Layered Architecture."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất xác định các tầng và nhóm các chức năng thành các component tương ứng. Quyết định: Tôi phân chia hệ thống theo Presentation, Business và Data Access Layer.</t>
+  </si>
+  <si>
+    <t>"Repository Pattern được thể hiện như thế nào trong Component Diagram?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho rằng Repository nên được mô hình hóa như các component riêng biệt và được Service sử dụng thông qua Interface. Quyết định: Tôi tạo các component BookingRepository và PaymentRepository riêng biệt.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra mối quan hệ giữa Service và Repository nên sử dụng loại UML relationship nào."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Dependency Relationship vì Service phụ thuộc vào Repository. Quyết định: Tôi sử dụng mũi tên Dependency trong sơ đồ.</t>
+  </si>
+  <si>
+    <t>"Đề xuất các component cho hệ thống AutoGo theo Layered Architecture."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất BookingUI, BookingService, PaymentService, CarRepository, BookingRepository và PaymentRepository. Quyết định: Tôi sử dụng cấu trúc này nhất quán với các UML Diagram khác.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Component Diagram và Deployment Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Component Diagram mô tả thành phần phần mềm, còn Deployment Diagram mô tả việc triển khai trên phần cứng hoặc máy chủ. Quyết định: Tôi hiểu rõ mục đích của từng loại sơ đồ UML.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra Component Diagram có tuân thủ Layered Architecture không."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện một số component Presentation truy cập trực tiếp Database. Quyết định: Tôi chỉnh sửa để mọi truy cập dữ liệu đi qua Service và Repository.</t>
+  </si>
+  <si>
+    <t>"Giải thích vai trò của Database trong Component Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cho biết Database thường được biểu diễn là thành phần lưu trữ dữ liệu và được Repository truy cập. Quyết định: Tôi kết nối Database với Repository thay vì kết nối trực tiếp với Service.</t>
+  </si>
+  <si>
+    <t>"Xác định các Interface cần có trong hệ thống AutoGo."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất IBookingRepository, ICarRepository và IPaymentRepository. Quyết định: Tôi sử dụng các interface này để thể hiện Repository Pattern rõ ràng hơn.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra việc sử dụng Interface có hợp lý không."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận xét Interface giúp giảm sự phụ thuộc trực tiếp giữa các component. Quyết định: Tôi giữ mô hình Interface để tăng khả năng mở rộng hệ thống.</t>
+  </si>
+  <si>
+    <t>"Mô tả luồng phụ thuộc giữa các component trong AutoGo."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất UI → Service → Repository → Database. Quyết định: Tôi sử dụng chuỗi phụ thuộc này trong Component Diagram.</t>
+  </si>
+  <si>
+    <t>"Phân biệt Dependency và Association trong Component Diagram."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích Component Diagram chủ yếu sử dụng Dependency thay vì Association. Quyết định: Tôi hạn chế dùng Association để đúng bản chất của sơ đồ thành phần.</t>
+  </si>
+  <si>
+    <t>"Những lỗi thường gặp khi vẽ Component Diagram là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI liệt kê các lỗi như thiếu Interface, kết nối sai tầng hoặc biểu diễn quá chi tiết như Class Diagram. Quyết định: Tôi sử dụng danh sách này để kiểm tra sơ đồ trước khi nộp.</t>
+  </si>
+  <si>
+    <t>"Tóm tắt quy trình xây dựng Component Diagram từ yêu cầu hệ thống."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất xác định kiến trúc, các component, interface và dependency. Quyết định: Tôi áp dụng quy trình này khi thiết kế hệ thống AutoGo.</t>
+  </si>
+  <si>
+    <t>"Tổng kết kiến thức về Component Diagram đã học."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI tổng hợp Component, Interface, Dependency, Repository Pattern và Layered Architecture. Quyết định: Tôi sử dụng các kiến thức này để xây dựng Component Diagram đúng chuẩn UML và phù hợp với yêu cầu bài thi.</t>
   </si>
 </sst>
 </file>
@@ -2859,9 +2979,309 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73658DE-3F57-4E46-A9B0-8E52C14BF266}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>